--- a/Harmonogram_nr_1_FEPW.01.01-IP.01-0825_26.xlsx
+++ b/Harmonogram_nr_1_FEPW.01.01-IP.01-0825_26.xlsx
@@ -571,7 +571,7 @@
         <v>17</v>
       </c>
       <c r="F2" s="5">
-        <v>195524.47</v>
+        <v>0</v>
       </c>
       <c r="G2" s="5">
         <v>239952.01</v>
@@ -597,7 +597,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="5">
-        <v>66095.94</v>
+        <v>0</v>
       </c>
       <c r="G3" s="5">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>7</v>
       </c>
       <c r="F4" s="5">
-        <v>56952.6</v>
+        <v>204667.81</v>
       </c>
       <c r="G4" s="5">
-        <v>239952.01</v>
+        <v>0</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -649,7 +649,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="5">
-        <v>56952.6</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
@@ -675,10 +675,10 @@
         <v>9</v>
       </c>
       <c r="F6" s="5">
-        <v>56952.6</v>
+        <v>0</v>
       </c>
       <c r="G6" s="5">
-        <v>0</v>
+        <v>239952.01</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -701,10 +701,10 @@
         <v>10</v>
       </c>
       <c r="F7" s="5">
-        <v>56952.6</v>
+        <v>170857.8</v>
       </c>
       <c r="G7" s="5">
-        <v>29994.01</v>
+        <v>0</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -727,7 +727,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="5">
-        <v>56952.6</v>
+        <v>0</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -753,7 +753,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="5">
-        <v>56952.6</v>
+        <v>0</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>13</v>
       </c>
       <c r="F10" s="5">
-        <v>51202.6</v>
+        <v>170857.8</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="5">
-        <v>51202.6</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>0</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="5">
-        <v>0</v>
+        <v>29994.01</v>
       </c>
       <c r="H12" s="5">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>16</v>
       </c>
       <c r="F13" s="5">
-        <v>0</v>
+        <v>159357.8</v>
       </c>
       <c r="G13" s="5">
         <v>0</v>
